--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4270"/>
+  <dimension ref="A1:F4271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85818,13 +85818,33 @@
         <v>172.75</v>
       </c>
       <c r="D4270" t="n">
-        <v>171.09</v>
+        <v>171.0899963378906</v>
       </c>
       <c r="E4270" t="n">
-        <v>171.26</v>
+        <v>171.2599945068359</v>
       </c>
       <c r="F4270" t="n">
         <v>2329673</v>
+      </c>
+    </row>
+    <row r="4271">
+      <c r="A4271" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B4271" t="n">
+        <v>173.8</v>
+      </c>
+      <c r="C4271" t="n">
+        <v>175.56</v>
+      </c>
+      <c r="D4271" t="n">
+        <v>173.62</v>
+      </c>
+      <c r="E4271" t="n">
+        <v>175.34</v>
+      </c>
+      <c r="F4271" t="n">
+        <v>400006</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -85832,19 +85832,19 @@
         <v>46231</v>
       </c>
       <c r="B4271" t="n">
-        <v>173.8</v>
+        <v>173.71</v>
       </c>
       <c r="C4271" t="n">
         <v>175.56</v>
       </c>
       <c r="D4271" t="n">
-        <v>173.62</v>
+        <v>173.52</v>
       </c>
       <c r="E4271" t="n">
         <v>175.34</v>
       </c>
       <c r="F4271" t="n">
-        <v>400006</v>
+        <v>862438</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -85832,19 +85832,19 @@
         <v>46231</v>
       </c>
       <c r="B4271" t="n">
-        <v>173.71</v>
+        <v>173.74</v>
       </c>
       <c r="C4271" t="n">
         <v>175.56</v>
       </c>
       <c r="D4271" t="n">
-        <v>173.52</v>
+        <v>173.33</v>
       </c>
       <c r="E4271" t="n">
         <v>175.34</v>
       </c>
       <c r="F4271" t="n">
-        <v>862438</v>
+        <v>1759430</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -85832,16 +85832,16 @@
         <v>46231</v>
       </c>
       <c r="B4271" t="n">
-        <v>173.74</v>
+        <v>173.7400054931641</v>
       </c>
       <c r="C4271" t="n">
-        <v>175.56</v>
+        <v>175.5599975585938</v>
       </c>
       <c r="D4271" t="n">
-        <v>173.33</v>
+        <v>173.3300018310547</v>
       </c>
       <c r="E4271" t="n">
-        <v>175.34</v>
+        <v>175.3399963378906</v>
       </c>
       <c r="F4271" t="n">
         <v>1759430</v>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4271"/>
+  <dimension ref="A1:F4272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85847,6 +85847,26 @@
         <v>1759430</v>
       </c>
     </row>
+    <row r="4272">
+      <c r="A4272" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B4272" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="C4272" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="D4272" t="n">
+        <v>171.28</v>
+      </c>
+      <c r="E4272" t="n">
+        <v>173.43</v>
+      </c>
+      <c r="F4272" t="n">
+        <v>1407282</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -85852,19 +85852,19 @@
         <v>46232</v>
       </c>
       <c r="B4272" t="n">
-        <v>171.6</v>
+        <v>170.55</v>
       </c>
       <c r="C4272" t="n">
         <v>173.5</v>
       </c>
       <c r="D4272" t="n">
-        <v>171.28</v>
+        <v>170.55</v>
       </c>
       <c r="E4272" t="n">
         <v>173.43</v>
       </c>
       <c r="F4272" t="n">
-        <v>1407282</v>
+        <v>3043225</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4272"/>
+  <dimension ref="A1:F4273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85852,19 +85852,39 @@
         <v>46232</v>
       </c>
       <c r="B4272" t="n">
-        <v>170.55</v>
+        <v>170.5500030517578</v>
       </c>
       <c r="C4272" t="n">
         <v>173.5</v>
       </c>
       <c r="D4272" t="n">
-        <v>170.55</v>
+        <v>170.5500030517578</v>
       </c>
       <c r="E4272" t="n">
-        <v>173.43</v>
+        <v>173.4299926757812</v>
       </c>
       <c r="F4272" t="n">
         <v>3043225</v>
+      </c>
+    </row>
+    <row r="4273">
+      <c r="A4273" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B4273" t="n">
+        <v>174.31</v>
+      </c>
+      <c r="C4273" t="n">
+        <v>174.31</v>
+      </c>
+      <c r="D4273" t="n">
+        <v>171.21</v>
+      </c>
+      <c r="E4273" t="n">
+        <v>171.45</v>
+      </c>
+      <c r="F4273" t="n">
+        <v>2575160</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4273"/>
+  <dimension ref="A1:F4274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85872,19 +85872,39 @@
         <v>46233</v>
       </c>
       <c r="B4273" t="n">
-        <v>174.31</v>
+        <v>174.3099975585938</v>
       </c>
       <c r="C4273" t="n">
-        <v>174.31</v>
+        <v>174.3099975585938</v>
       </c>
       <c r="D4273" t="n">
-        <v>171.21</v>
+        <v>171.2100067138672</v>
       </c>
       <c r="E4273" t="n">
-        <v>171.45</v>
+        <v>171.4499969482422</v>
       </c>
       <c r="F4273" t="n">
         <v>2575160</v>
+      </c>
+    </row>
+    <row r="4274">
+      <c r="A4274" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B4274" t="n">
+        <v>175.02</v>
+      </c>
+      <c r="C4274" t="n">
+        <v>175.69</v>
+      </c>
+      <c r="D4274" t="n">
+        <v>174.48</v>
+      </c>
+      <c r="E4274" t="n">
+        <v>175.09</v>
+      </c>
+      <c r="F4274" t="n">
+        <v>1727771</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4274"/>
+  <dimension ref="A1:F4275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85892,19 +85892,39 @@
         <v>46234</v>
       </c>
       <c r="B4274" t="n">
-        <v>175.02</v>
+        <v>175.0200042724609</v>
       </c>
       <c r="C4274" t="n">
-        <v>175.69</v>
+        <v>175.6900024414062</v>
       </c>
       <c r="D4274" t="n">
-        <v>174.48</v>
+        <v>174.4799957275391</v>
       </c>
       <c r="E4274" t="n">
-        <v>175.09</v>
+        <v>175.0899963378906</v>
       </c>
       <c r="F4274" t="n">
-        <v>1727771</v>
+        <v>1733689</v>
+      </c>
+    </row>
+    <row r="4275">
+      <c r="A4275" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B4275" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="C4275" t="n">
+        <v>175.67</v>
+      </c>
+      <c r="D4275" t="n">
+        <v>173.78</v>
+      </c>
+      <c r="E4275" t="n">
+        <v>175.53</v>
+      </c>
+      <c r="F4275" t="n">
+        <v>1426378</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4275"/>
+  <dimension ref="A1:F4276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85912,19 +85912,39 @@
         <v>46237</v>
       </c>
       <c r="B4275" t="n">
-        <v>174.9</v>
+        <v>174.8999938964844</v>
       </c>
       <c r="C4275" t="n">
-        <v>175.67</v>
+        <v>175.6699981689453</v>
       </c>
       <c r="D4275" t="n">
-        <v>173.78</v>
+        <v>173.7799987792969</v>
       </c>
       <c r="E4275" t="n">
-        <v>175.53</v>
+        <v>175.5299987792969</v>
       </c>
       <c r="F4275" t="n">
         <v>1426378</v>
+      </c>
+    </row>
+    <row r="4276">
+      <c r="A4276" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B4276" t="n">
+        <v>174.85</v>
+      </c>
+      <c r="C4276" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="D4276" t="n">
+        <v>174.46</v>
+      </c>
+      <c r="E4276" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="F4276" t="n">
+        <v>2801983</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4276"/>
+  <dimension ref="A1:F4277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85932,19 +85932,39 @@
         <v>46238</v>
       </c>
       <c r="B4276" t="n">
-        <v>174.85</v>
+        <v>174.8500061035156</v>
       </c>
       <c r="C4276" t="n">
         <v>177.75</v>
       </c>
       <c r="D4276" t="n">
-        <v>174.46</v>
+        <v>174.4600067138672</v>
       </c>
       <c r="E4276" t="n">
-        <v>177.2</v>
+        <v>177.1999969482422</v>
       </c>
       <c r="F4276" t="n">
         <v>2801983</v>
+      </c>
+    </row>
+    <row r="4277">
+      <c r="A4277" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B4277" t="n">
+        <v>174.7</v>
+      </c>
+      <c r="C4277" t="n">
+        <v>177.21</v>
+      </c>
+      <c r="D4277" t="n">
+        <v>174.59</v>
+      </c>
+      <c r="E4277" t="n">
+        <v>175.53</v>
+      </c>
+      <c r="F4277" t="n">
+        <v>2469125</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4277"/>
+  <dimension ref="A1:F4278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85952,19 +85952,39 @@
         <v>46239</v>
       </c>
       <c r="B4277" t="n">
-        <v>174.7</v>
+        <v>174.6999969482422</v>
       </c>
       <c r="C4277" t="n">
-        <v>177.21</v>
+        <v>177.2100067138672</v>
       </c>
       <c r="D4277" t="n">
-        <v>174.59</v>
+        <v>174.5899963378906</v>
       </c>
       <c r="E4277" t="n">
-        <v>175.53</v>
+        <v>175.5299987792969</v>
       </c>
       <c r="F4277" t="n">
         <v>2469125</v>
+      </c>
+    </row>
+    <row r="4278">
+      <c r="A4278" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B4278" t="n">
+        <v>172.04</v>
+      </c>
+      <c r="C4278" t="n">
+        <v>174.63</v>
+      </c>
+      <c r="D4278" t="n">
+        <v>172.04</v>
+      </c>
+      <c r="E4278" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="F4278" t="n">
+        <v>3363032</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4278"/>
+  <dimension ref="A1:F4279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85972,19 +85972,39 @@
         <v>46240</v>
       </c>
       <c r="B4278" t="n">
-        <v>172.04</v>
+        <v>172.0399932861328</v>
       </c>
       <c r="C4278" t="n">
-        <v>174.63</v>
+        <v>174.6300048828125</v>
       </c>
       <c r="D4278" t="n">
-        <v>172.04</v>
+        <v>172.0399932861328</v>
       </c>
       <c r="E4278" t="n">
         <v>173.5</v>
       </c>
       <c r="F4278" t="n">
         <v>3363032</v>
+      </c>
+    </row>
+    <row r="4279">
+      <c r="A4279" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B4279" t="n">
+        <v>169.37</v>
+      </c>
+      <c r="C4279" t="n">
+        <v>173.13</v>
+      </c>
+      <c r="D4279" t="n">
+        <v>169.15</v>
+      </c>
+      <c r="E4279" t="n">
+        <v>172.82</v>
+      </c>
+      <c r="F4279" t="n">
+        <v>4045013</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4279"/>
+  <dimension ref="A1:F4280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85992,19 +85992,39 @@
         <v>46241</v>
       </c>
       <c r="B4279" t="n">
-        <v>169.37</v>
+        <v>169.3699951171875</v>
       </c>
       <c r="C4279" t="n">
-        <v>173.13</v>
+        <v>173.1300048828125</v>
       </c>
       <c r="D4279" t="n">
-        <v>169.15</v>
+        <v>169.1499938964844</v>
       </c>
       <c r="E4279" t="n">
-        <v>172.82</v>
+        <v>172.8200073242188</v>
       </c>
       <c r="F4279" t="n">
         <v>4045013</v>
+      </c>
+    </row>
+    <row r="4280">
+      <c r="A4280" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B4280" t="n">
+        <v>169.27</v>
+      </c>
+      <c r="C4280" t="n">
+        <v>170.11</v>
+      </c>
+      <c r="D4280" t="n">
+        <v>168.63</v>
+      </c>
+      <c r="E4280" t="n">
+        <v>169.54</v>
+      </c>
+      <c r="F4280" t="n">
+        <v>5195835</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4280"/>
+  <dimension ref="A1:F4281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86012,19 +86012,39 @@
         <v>46244</v>
       </c>
       <c r="B4280" t="n">
-        <v>169.27</v>
+        <v>169.2700042724609</v>
       </c>
       <c r="C4280" t="n">
-        <v>170.11</v>
+        <v>170.1100006103516</v>
       </c>
       <c r="D4280" t="n">
-        <v>168.63</v>
+        <v>168.6300048828125</v>
       </c>
       <c r="E4280" t="n">
-        <v>169.54</v>
+        <v>169.5399932861328</v>
       </c>
       <c r="F4280" t="n">
         <v>5195835</v>
+      </c>
+    </row>
+    <row r="4281">
+      <c r="A4281" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B4281" t="n">
+        <v>165.05</v>
+      </c>
+      <c r="C4281" t="n">
+        <v>169.41</v>
+      </c>
+      <c r="D4281" t="n">
+        <v>164.69</v>
+      </c>
+      <c r="E4281" t="n">
+        <v>169.41</v>
+      </c>
+      <c r="F4281" t="n">
+        <v>7129443</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4281"/>
+  <dimension ref="A1:F4282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86032,19 +86032,39 @@
         <v>46245</v>
       </c>
       <c r="B4281" t="n">
-        <v>165.05</v>
+        <v>165.0500030517578</v>
       </c>
       <c r="C4281" t="n">
-        <v>169.41</v>
+        <v>169.4100036621094</v>
       </c>
       <c r="D4281" t="n">
-        <v>164.69</v>
+        <v>164.6900024414062</v>
       </c>
       <c r="E4281" t="n">
-        <v>169.41</v>
+        <v>169.4100036621094</v>
       </c>
       <c r="F4281" t="n">
         <v>7129443</v>
+      </c>
+    </row>
+    <row r="4282">
+      <c r="A4282" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B4282" t="n">
+        <v>164.67</v>
+      </c>
+      <c r="C4282" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="D4282" t="n">
+        <v>164.34</v>
+      </c>
+      <c r="E4282" t="n">
+        <v>165.27</v>
+      </c>
+      <c r="F4282" t="n">
+        <v>2519475</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4282"/>
+  <dimension ref="A1:F4283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86052,19 +86052,39 @@
         <v>46246</v>
       </c>
       <c r="B4282" t="n">
-        <v>164.67</v>
+        <v>164.6699981689453</v>
       </c>
       <c r="C4282" t="n">
-        <v>165.6</v>
+        <v>165.6000061035156</v>
       </c>
       <c r="D4282" t="n">
-        <v>164.34</v>
+        <v>164.3399963378906</v>
       </c>
       <c r="E4282" t="n">
-        <v>165.27</v>
+        <v>165.2700042724609</v>
       </c>
       <c r="F4282" t="n">
         <v>2519475</v>
+      </c>
+    </row>
+    <row r="4283">
+      <c r="A4283" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B4283" t="n">
+        <v>164.15</v>
+      </c>
+      <c r="C4283" t="n">
+        <v>165.72</v>
+      </c>
+      <c r="D4283" t="n">
+        <v>163.43</v>
+      </c>
+      <c r="E4283" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="F4283" t="n">
+        <v>1300969</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4283"/>
+  <dimension ref="A1:F4284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86071,20 +86071,32 @@
       <c r="A4283" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="B4283" t="n">
-        <v>164.15</v>
-      </c>
-      <c r="C4283" t="n">
-        <v>165.72</v>
-      </c>
-      <c r="D4283" t="n">
-        <v>163.43</v>
-      </c>
-      <c r="E4283" t="n">
-        <v>164.4</v>
-      </c>
+      <c r="B4283" t="inlineStr"/>
+      <c r="C4283" t="inlineStr"/>
+      <c r="D4283" t="inlineStr"/>
+      <c r="E4283" t="inlineStr"/>
       <c r="F4283" t="n">
-        <v>1300969</v>
+        <v>3331500</v>
+      </c>
+    </row>
+    <row r="4284">
+      <c r="A4284" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B4284" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="C4284" t="n">
+        <v>164.14</v>
+      </c>
+      <c r="D4284" t="n">
+        <v>162.07</v>
+      </c>
+      <c r="E4284" t="n">
+        <v>163.73</v>
+      </c>
+      <c r="F4284" t="n">
+        <v>3338219</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4284"/>
+  <dimension ref="A1:F4285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86071,12 +86071,20 @@
       <c r="A4283" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="B4283" t="inlineStr"/>
-      <c r="C4283" t="inlineStr"/>
-      <c r="D4283" t="inlineStr"/>
-      <c r="E4283" t="inlineStr"/>
+      <c r="B4283" t="n">
+        <v>164.1499938964844</v>
+      </c>
+      <c r="C4283" t="n">
+        <v>165.7200012207031</v>
+      </c>
+      <c r="D4283" t="n">
+        <v>163.4299926757812</v>
+      </c>
+      <c r="E4283" t="n">
+        <v>164.3999938964844</v>
+      </c>
       <c r="F4283" t="n">
-        <v>3331500</v>
+        <v>1300969</v>
       </c>
     </row>
     <row r="4284">
@@ -86084,19 +86092,39 @@
         <v>46248</v>
       </c>
       <c r="B4284" t="n">
-        <v>163.9</v>
+        <v>163.8999938964844</v>
       </c>
       <c r="C4284" t="n">
-        <v>164.14</v>
+        <v>164.1399993896484</v>
       </c>
       <c r="D4284" t="n">
-        <v>162.07</v>
+        <v>162.0700073242188</v>
       </c>
       <c r="E4284" t="n">
-        <v>163.73</v>
+        <v>163.7299957275391</v>
       </c>
       <c r="F4284" t="n">
-        <v>3338219</v>
+        <v>3342021</v>
+      </c>
+    </row>
+    <row r="4285">
+      <c r="A4285" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B4285" t="n">
+        <v>163.8</v>
+      </c>
+      <c r="C4285" t="n">
+        <v>165.19</v>
+      </c>
+      <c r="D4285" t="n">
+        <v>163.64</v>
+      </c>
+      <c r="E4285" t="n">
+        <v>164.11</v>
+      </c>
+      <c r="F4285" t="n">
+        <v>2971451</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4285"/>
+  <dimension ref="A1:F4286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86112,19 +86112,39 @@
         <v>46251</v>
       </c>
       <c r="B4285" t="n">
-        <v>163.8</v>
+        <v>163.8000030517578</v>
       </c>
       <c r="C4285" t="n">
-        <v>165.19</v>
+        <v>165.1900024414062</v>
       </c>
       <c r="D4285" t="n">
-        <v>163.64</v>
+        <v>163.6399993896484</v>
       </c>
       <c r="E4285" t="n">
-        <v>164.11</v>
+        <v>164.1100006103516</v>
       </c>
       <c r="F4285" t="n">
         <v>2971451</v>
+      </c>
+    </row>
+    <row r="4286">
+      <c r="A4286" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B4286" t="n">
+        <v>163.55</v>
+      </c>
+      <c r="C4286" t="n">
+        <v>165.62</v>
+      </c>
+      <c r="D4286" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="E4286" t="n">
+        <v>164.05</v>
+      </c>
+      <c r="F4286" t="n">
+        <v>2455703</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4286"/>
+  <dimension ref="A1:F4287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86131,20 +86131,32 @@
       <c r="A4286" s="1" t="n">
         <v>46252</v>
       </c>
-      <c r="B4286" t="n">
-        <v>163.55</v>
-      </c>
-      <c r="C4286" t="n">
-        <v>165.62</v>
-      </c>
-      <c r="D4286" t="n">
-        <v>163.2</v>
-      </c>
-      <c r="E4286" t="n">
-        <v>164.05</v>
-      </c>
+      <c r="B4286" t="inlineStr"/>
+      <c r="C4286" t="inlineStr"/>
+      <c r="D4286" t="inlineStr"/>
+      <c r="E4286" t="inlineStr"/>
       <c r="F4286" t="n">
-        <v>2455703</v>
+        <v>3862610</v>
+      </c>
+    </row>
+    <row r="4287">
+      <c r="A4287" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B4287" t="n">
+        <v>165</v>
+      </c>
+      <c r="C4287" t="n">
+        <v>167.59</v>
+      </c>
+      <c r="D4287" t="n">
+        <v>164.68</v>
+      </c>
+      <c r="E4287" t="n">
+        <v>166.22</v>
+      </c>
+      <c r="F4287" t="n">
+        <v>3865016</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4287"/>
+  <dimension ref="A1:F4288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86131,12 +86131,20 @@
       <c r="A4286" s="1" t="n">
         <v>46252</v>
       </c>
-      <c r="B4286" t="inlineStr"/>
-      <c r="C4286" t="inlineStr"/>
-      <c r="D4286" t="inlineStr"/>
-      <c r="E4286" t="inlineStr"/>
+      <c r="B4286" t="n">
+        <v>163.5500030517578</v>
+      </c>
+      <c r="C4286" t="n">
+        <v>165.6199951171875</v>
+      </c>
+      <c r="D4286" t="n">
+        <v>163.4400024414062</v>
+      </c>
+      <c r="E4286" t="n">
+        <v>164.0500030517578</v>
+      </c>
       <c r="F4286" t="n">
-        <v>3862610</v>
+        <v>2455703</v>
       </c>
     </row>
     <row r="4287">
@@ -86147,16 +86155,36 @@
         <v>165</v>
       </c>
       <c r="C4287" t="n">
-        <v>167.59</v>
+        <v>167.5899963378906</v>
       </c>
       <c r="D4287" t="n">
-        <v>164.68</v>
+        <v>164.6799926757812</v>
       </c>
       <c r="E4287" t="n">
-        <v>166.22</v>
+        <v>166.2200012207031</v>
       </c>
       <c r="F4287" t="n">
         <v>3865016</v>
+      </c>
+    </row>
+    <row r="4288">
+      <c r="A4288" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B4288" t="n">
+        <v>165</v>
+      </c>
+      <c r="C4288" t="n">
+        <v>166.99</v>
+      </c>
+      <c r="D4288" t="n">
+        <v>164.14</v>
+      </c>
+      <c r="E4288" t="n">
+        <v>164.3</v>
+      </c>
+      <c r="F4288" t="n">
+        <v>5532280</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4288"/>
+  <dimension ref="A1:F4289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86175,16 +86175,36 @@
         <v>165</v>
       </c>
       <c r="C4288" t="n">
-        <v>166.99</v>
+        <v>166.9900054931641</v>
       </c>
       <c r="D4288" t="n">
-        <v>164.14</v>
+        <v>164.1399993896484</v>
       </c>
       <c r="E4288" t="n">
-        <v>164.3</v>
+        <v>164.3000030517578</v>
       </c>
       <c r="F4288" t="n">
         <v>5532280</v>
+      </c>
+    </row>
+    <row r="4289">
+      <c r="A4289" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B4289" t="n">
+        <v>168.33</v>
+      </c>
+      <c r="C4289" t="n">
+        <v>169.25</v>
+      </c>
+      <c r="D4289" t="n">
+        <v>165.71</v>
+      </c>
+      <c r="E4289" t="n">
+        <v>166.11</v>
+      </c>
+      <c r="F4289" t="n">
+        <v>7494178</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4289"/>
+  <dimension ref="A1:F4290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86192,19 +86192,39 @@
         <v>46255</v>
       </c>
       <c r="B4289" t="n">
-        <v>168.33</v>
+        <v>168.3300018310547</v>
       </c>
       <c r="C4289" t="n">
         <v>169.25</v>
       </c>
       <c r="D4289" t="n">
-        <v>165.71</v>
+        <v>165.7100067138672</v>
       </c>
       <c r="E4289" t="n">
-        <v>166.11</v>
+        <v>166.1100006103516</v>
       </c>
       <c r="F4289" t="n">
-        <v>7494178</v>
+        <v>7491177</v>
+      </c>
+    </row>
+    <row r="4290">
+      <c r="A4290" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B4290" t="n">
+        <v>169.01</v>
+      </c>
+      <c r="C4290" t="n">
+        <v>170.43</v>
+      </c>
+      <c r="D4290" t="n">
+        <v>166.49</v>
+      </c>
+      <c r="E4290" t="n">
+        <v>167</v>
+      </c>
+      <c r="F4290" t="n">
+        <v>3801187</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4290"/>
+  <dimension ref="A1:F4291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86211,20 +86211,32 @@
       <c r="A4290" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="B4290" t="n">
+      <c r="B4290" t="inlineStr"/>
+      <c r="C4290" t="inlineStr"/>
+      <c r="D4290" t="inlineStr"/>
+      <c r="E4290" t="inlineStr"/>
+      <c r="F4290" t="n">
+        <v>7183848</v>
+      </c>
+    </row>
+    <row r="4291">
+      <c r="A4291" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B4291" t="n">
+        <v>171.88</v>
+      </c>
+      <c r="C4291" t="n">
+        <v>172.17</v>
+      </c>
+      <c r="D4291" t="n">
+        <v>168.42</v>
+      </c>
+      <c r="E4291" t="n">
         <v>169.01</v>
       </c>
-      <c r="C4290" t="n">
-        <v>170.43</v>
-      </c>
-      <c r="D4290" t="n">
-        <v>166.49</v>
-      </c>
-      <c r="E4290" t="n">
-        <v>167</v>
-      </c>
-      <c r="F4290" t="n">
-        <v>3801187</v>
+      <c r="F4291" t="n">
+        <v>7189996</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4291"/>
+  <dimension ref="A1:F4292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86211,12 +86211,20 @@
       <c r="A4290" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="B4290" t="inlineStr"/>
-      <c r="C4290" t="inlineStr"/>
-      <c r="D4290" t="inlineStr"/>
-      <c r="E4290" t="inlineStr"/>
+      <c r="B4290" t="n">
+        <v>169.0099945068359</v>
+      </c>
+      <c r="C4290" t="n">
+        <v>170.4299926757812</v>
+      </c>
+      <c r="D4290" t="n">
+        <v>166.4900054931641</v>
+      </c>
+      <c r="E4290" t="n">
+        <v>167</v>
+      </c>
       <c r="F4290" t="n">
-        <v>7183848</v>
+        <v>3801187</v>
       </c>
     </row>
     <row r="4291">
@@ -86224,19 +86232,39 @@
         <v>46259</v>
       </c>
       <c r="B4291" t="n">
-        <v>171.88</v>
+        <v>171.8800048828125</v>
       </c>
       <c r="C4291" t="n">
-        <v>172.17</v>
+        <v>172.1699981689453</v>
       </c>
       <c r="D4291" t="n">
-        <v>168.42</v>
+        <v>168.4199981689453</v>
       </c>
       <c r="E4291" t="n">
-        <v>169.01</v>
+        <v>169.0099945068359</v>
       </c>
       <c r="F4291" t="n">
         <v>7189996</v>
+      </c>
+    </row>
+    <row r="4292">
+      <c r="A4292" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B4292" t="n">
+        <v>171.8200073242188</v>
+      </c>
+      <c r="C4292" t="n">
+        <v>173.5899963378906</v>
+      </c>
+      <c r="D4292" t="n">
+        <v>171.4400024414062</v>
+      </c>
+      <c r="E4292" t="n">
+        <v>172.1100006103516</v>
+      </c>
+      <c r="F4292" t="n">
+        <v>2549726</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4292"/>
+  <dimension ref="A1:F4293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86204,7 +86204,7 @@
         <v>166.1100006103516</v>
       </c>
       <c r="F4289" t="n">
-        <v>7491177</v>
+        <v>7503932</v>
       </c>
     </row>
     <row r="4290">
@@ -86264,7 +86264,27 @@
         <v>172.1100006103516</v>
       </c>
       <c r="F4292" t="n">
-        <v>2549726</v>
+        <v>2782364</v>
+      </c>
+    </row>
+    <row r="4293">
+      <c r="A4293" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B4293" t="n">
+        <v>172.4</v>
+      </c>
+      <c r="C4293" t="n">
+        <v>172.8</v>
+      </c>
+      <c r="D4293" t="n">
+        <v>170.82</v>
+      </c>
+      <c r="E4293" t="n">
+        <v>170.98</v>
+      </c>
+      <c r="F4293" t="n">
+        <v>4480946</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4293"/>
+  <dimension ref="A1:F4294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86204,7 +86204,7 @@
         <v>166.1100006103516</v>
       </c>
       <c r="F4289" t="n">
-        <v>7503932</v>
+        <v>7491177</v>
       </c>
     </row>
     <row r="4290">
@@ -86271,20 +86271,32 @@
       <c r="A4293" s="1" t="n">
         <v>46261</v>
       </c>
-      <c r="B4293" t="n">
-        <v>172.4</v>
-      </c>
-      <c r="C4293" t="n">
-        <v>172.8</v>
-      </c>
-      <c r="D4293" t="n">
-        <v>170.82</v>
-      </c>
-      <c r="E4293" t="n">
-        <v>170.98</v>
-      </c>
+      <c r="B4293" t="inlineStr"/>
+      <c r="C4293" t="inlineStr"/>
+      <c r="D4293" t="inlineStr"/>
+      <c r="E4293" t="inlineStr"/>
       <c r="F4293" t="n">
-        <v>4480946</v>
+        <v>2484584</v>
+      </c>
+    </row>
+    <row r="4294">
+      <c r="A4294" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B4294" t="n">
+        <v>171.92</v>
+      </c>
+      <c r="C4294" t="n">
+        <v>173.69</v>
+      </c>
+      <c r="D4294" t="n">
+        <v>171.11</v>
+      </c>
+      <c r="E4294" t="n">
+        <v>173.04</v>
+      </c>
+      <c r="F4294" t="n">
+        <v>2484593</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -86276,7 +86276,7 @@
       <c r="D4293" t="inlineStr"/>
       <c r="E4293" t="inlineStr"/>
       <c r="F4293" t="n">
-        <v>2484584</v>
+        <v>3710421</v>
       </c>
     </row>
     <row r="4294">
@@ -86284,7 +86284,7 @@
         <v>46262</v>
       </c>
       <c r="B4294" t="n">
-        <v>171.92</v>
+        <v>172.72</v>
       </c>
       <c r="C4294" t="n">
         <v>173.69</v>
@@ -86296,7 +86296,7 @@
         <v>173.04</v>
       </c>
       <c r="F4294" t="n">
-        <v>2484593</v>
+        <v>3710421</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4294"/>
+  <dimension ref="A1:F4293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86269,7 +86269,7 @@
     </row>
     <row r="4293">
       <c r="A4293" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B4293" t="inlineStr"/>
       <c r="C4293" t="inlineStr"/>
@@ -86279,26 +86279,6 @@
         <v>3710421</v>
       </c>
     </row>
-    <row r="4294">
-      <c r="A4294" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B4294" t="n">
-        <v>172.72</v>
-      </c>
-      <c r="C4294" t="n">
-        <v>173.69</v>
-      </c>
-      <c r="D4294" t="n">
-        <v>171.11</v>
-      </c>
-      <c r="E4294" t="n">
-        <v>173.04</v>
-      </c>
-      <c r="F4294" t="n">
-        <v>3710421</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4293"/>
+  <dimension ref="A1:F4296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86204,7 +86204,7 @@
         <v>166.1100006103516</v>
       </c>
       <c r="F4289" t="n">
-        <v>7491177</v>
+        <v>7503932</v>
       </c>
     </row>
     <row r="4290">
@@ -86269,14 +86269,82 @@
     </row>
     <row r="4293">
       <c r="A4293" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B4293" t="n">
+        <v>172.3999938964844</v>
+      </c>
+      <c r="C4293" t="n">
+        <v>172.8000030517578</v>
+      </c>
+      <c r="D4293" t="n">
+        <v>170.8200073242188</v>
+      </c>
+      <c r="E4293" t="n">
+        <v>170.9799957275391</v>
+      </c>
+      <c r="F4293" t="n">
+        <v>4480946</v>
+      </c>
+    </row>
+    <row r="4294">
+      <c r="A4294" s="1" t="n">
         <v>46262</v>
       </c>
-      <c r="B4293" t="inlineStr"/>
-      <c r="C4293" t="inlineStr"/>
-      <c r="D4293" t="inlineStr"/>
-      <c r="E4293" t="inlineStr"/>
-      <c r="F4293" t="n">
-        <v>3710421</v>
+      <c r="B4294" t="n">
+        <v>172.7200012207031</v>
+      </c>
+      <c r="C4294" t="n">
+        <v>173.6900024414062</v>
+      </c>
+      <c r="D4294" t="n">
+        <v>171.1100006103516</v>
+      </c>
+      <c r="E4294" t="n">
+        <v>173.0399932861328</v>
+      </c>
+      <c r="F4294" t="n">
+        <v>3751418</v>
+      </c>
+    </row>
+    <row r="4295">
+      <c r="A4295" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B4295" t="n">
+        <v>174.7799987792969</v>
+      </c>
+      <c r="C4295" t="n">
+        <v>175.8000030517578</v>
+      </c>
+      <c r="D4295" t="n">
+        <v>174.0599975585938</v>
+      </c>
+      <c r="E4295" t="n">
+        <v>175.2700042724609</v>
+      </c>
+      <c r="F4295" t="n">
+        <v>5448044</v>
+      </c>
+    </row>
+    <row r="4296">
+      <c r="A4296" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B4296" t="n">
+        <v>177.1</v>
+      </c>
+      <c r="C4296" t="n">
+        <v>178.25</v>
+      </c>
+      <c r="D4296" t="n">
+        <v>174.48</v>
+      </c>
+      <c r="E4296" t="n">
+        <v>175.47</v>
+      </c>
+      <c r="F4296" t="n">
+        <v>5629246</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4296"/>
+  <dimension ref="A1:F4297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86331,20 +86331,32 @@
       <c r="A4296" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B4296" t="n">
-        <v>177.1</v>
-      </c>
-      <c r="C4296" t="n">
+      <c r="B4296" t="inlineStr"/>
+      <c r="C4296" t="inlineStr"/>
+      <c r="D4296" t="inlineStr"/>
+      <c r="E4296" t="inlineStr"/>
+      <c r="F4296" t="n">
+        <v>5081986</v>
+      </c>
+    </row>
+    <row r="4297">
+      <c r="A4297" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B4297" t="n">
+        <v>182.27</v>
+      </c>
+      <c r="C4297" t="n">
+        <v>183.37</v>
+      </c>
+      <c r="D4297" t="n">
+        <v>177.38</v>
+      </c>
+      <c r="E4297" t="n">
         <v>178.25</v>
       </c>
-      <c r="D4296" t="n">
-        <v>174.48</v>
-      </c>
-      <c r="E4296" t="n">
-        <v>175.47</v>
-      </c>
-      <c r="F4296" t="n">
-        <v>5629246</v>
+      <c r="F4297" t="n">
+        <v>5116457</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4297"/>
+  <dimension ref="A1:F4298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86331,12 +86331,20 @@
       <c r="A4296" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B4296" t="inlineStr"/>
-      <c r="C4296" t="inlineStr"/>
-      <c r="D4296" t="inlineStr"/>
-      <c r="E4296" t="inlineStr"/>
+      <c r="B4296" t="n">
+        <v>177.1000061035156</v>
+      </c>
+      <c r="C4296" t="n">
+        <v>178.25</v>
+      </c>
+      <c r="D4296" t="n">
+        <v>174.4799957275391</v>
+      </c>
+      <c r="E4296" t="n">
+        <v>175.4700012207031</v>
+      </c>
       <c r="F4296" t="n">
-        <v>5081986</v>
+        <v>5629246</v>
       </c>
     </row>
     <row r="4297">
@@ -86344,19 +86352,39 @@
         <v>46267</v>
       </c>
       <c r="B4297" t="n">
-        <v>182.27</v>
+        <v>182.2700042724609</v>
       </c>
       <c r="C4297" t="n">
-        <v>183.37</v>
+        <v>183.3600006103516</v>
       </c>
       <c r="D4297" t="n">
-        <v>177.38</v>
+        <v>177.3800048828125</v>
       </c>
       <c r="E4297" t="n">
         <v>178.25</v>
       </c>
       <c r="F4297" t="n">
         <v>5116457</v>
+      </c>
+    </row>
+    <row r="4298">
+      <c r="A4298" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B4298" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="C4298" t="n">
+        <v>186.01</v>
+      </c>
+      <c r="D4298" t="n">
+        <v>181.88</v>
+      </c>
+      <c r="E4298" t="n">
+        <v>184.54</v>
+      </c>
+      <c r="F4298" t="n">
+        <v>4512953</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4298"/>
+  <dimension ref="A1:F4299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86371,20 +86371,32 @@
       <c r="A4298" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B4298" t="n">
-        <v>182.25</v>
-      </c>
-      <c r="C4298" t="n">
-        <v>186.01</v>
-      </c>
-      <c r="D4298" t="n">
-        <v>181.88</v>
-      </c>
-      <c r="E4298" t="n">
-        <v>184.54</v>
-      </c>
+      <c r="B4298" t="inlineStr"/>
+      <c r="C4298" t="inlineStr"/>
+      <c r="D4298" t="inlineStr"/>
+      <c r="E4298" t="inlineStr"/>
       <c r="F4298" t="n">
-        <v>4512953</v>
+        <v>2472573</v>
+      </c>
+    </row>
+    <row r="4299">
+      <c r="A4299" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B4299" t="n">
+        <v>181.94</v>
+      </c>
+      <c r="C4299" t="n">
+        <v>183.63</v>
+      </c>
+      <c r="D4299" t="n">
+        <v>180.29</v>
+      </c>
+      <c r="E4299" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="F4299" t="n">
+        <v>2491912</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -86371,12 +86371,20 @@
       <c r="A4298" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B4298" t="inlineStr"/>
-      <c r="C4298" t="inlineStr"/>
-      <c r="D4298" t="inlineStr"/>
-      <c r="E4298" t="inlineStr"/>
+      <c r="B4298" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="C4298" t="n">
+        <v>186.0099945068359</v>
+      </c>
+      <c r="D4298" t="n">
+        <v>181.8800048828125</v>
+      </c>
+      <c r="E4298" t="n">
+        <v>184.5399932861328</v>
+      </c>
       <c r="F4298" t="n">
-        <v>2472573</v>
+        <v>4512953</v>
       </c>
     </row>
     <row r="4299">
@@ -86384,16 +86392,16 @@
         <v>46269</v>
       </c>
       <c r="B4299" t="n">
-        <v>181.94</v>
+        <v>181.9400024414062</v>
       </c>
       <c r="C4299" t="n">
-        <v>183.63</v>
+        <v>183.6300048828125</v>
       </c>
       <c r="D4299" t="n">
-        <v>180.29</v>
+        <v>180.2899932861328</v>
       </c>
       <c r="E4299" t="n">
-        <v>181.7</v>
+        <v>181.6999969482422</v>
       </c>
       <c r="F4299" t="n">
         <v>2491912</v>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4299"/>
+  <dimension ref="A1:F4300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86407,6 +86407,26 @@
         <v>2491912</v>
       </c>
     </row>
+    <row r="4300">
+      <c r="A4300" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B4300" t="n">
+        <v>184.79</v>
+      </c>
+      <c r="C4300" t="n">
+        <v>186.6</v>
+      </c>
+      <c r="D4300" t="n">
+        <v>184.31</v>
+      </c>
+      <c r="E4300" t="n">
+        <v>184.73</v>
+      </c>
+      <c r="F4300" t="n">
+        <v>3559575</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4300"/>
+  <dimension ref="A1:F4301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86427,6 +86427,26 @@
         <v>3559575</v>
       </c>
     </row>
+    <row r="4301">
+      <c r="A4301" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B4301" t="n">
+        <v>182.87</v>
+      </c>
+      <c r="C4301" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="D4301" t="n">
+        <v>181.82</v>
+      </c>
+      <c r="E4301" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="F4301" t="n">
+        <v>3474896</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4301"/>
+  <dimension ref="A1:F4302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86412,16 +86412,16 @@
         <v>46273</v>
       </c>
       <c r="B4300" t="n">
-        <v>184.79</v>
+        <v>184.7899932861328</v>
       </c>
       <c r="C4300" t="n">
-        <v>186.6</v>
+        <v>186.6000061035156</v>
       </c>
       <c r="D4300" t="n">
-        <v>184.31</v>
+        <v>184.3099975585938</v>
       </c>
       <c r="E4300" t="n">
-        <v>184.73</v>
+        <v>184.7299957275391</v>
       </c>
       <c r="F4300" t="n">
         <v>3559575</v>
@@ -86432,19 +86432,39 @@
         <v>46274</v>
       </c>
       <c r="B4301" t="n">
-        <v>182.87</v>
+        <v>182.8699951171875</v>
       </c>
       <c r="C4301" t="n">
         <v>184.25</v>
       </c>
       <c r="D4301" t="n">
-        <v>181.82</v>
+        <v>181.8200073242188</v>
       </c>
       <c r="E4301" t="n">
-        <v>183.7</v>
+        <v>183.6999969482422</v>
       </c>
       <c r="F4301" t="n">
         <v>3474896</v>
+      </c>
+    </row>
+    <row r="4302">
+      <c r="A4302" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B4302" t="n">
+        <v>185.21</v>
+      </c>
+      <c r="C4302" t="n">
+        <v>185.67</v>
+      </c>
+      <c r="D4302" t="n">
+        <v>181.59</v>
+      </c>
+      <c r="E4302" t="n">
+        <v>182.26</v>
+      </c>
+      <c r="F4302" t="n">
+        <v>3906254</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4302"/>
+  <dimension ref="A1:F4303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86452,19 +86452,39 @@
         <v>46275</v>
       </c>
       <c r="B4302" t="n">
-        <v>185.21</v>
+        <v>185.2100067138672</v>
       </c>
       <c r="C4302" t="n">
-        <v>185.67</v>
+        <v>185.6699981689453</v>
       </c>
       <c r="D4302" t="n">
-        <v>181.59</v>
+        <v>181.5899963378906</v>
       </c>
       <c r="E4302" t="n">
-        <v>182.26</v>
+        <v>182.2599945068359</v>
       </c>
       <c r="F4302" t="n">
         <v>3906254</v>
+      </c>
+    </row>
+    <row r="4303">
+      <c r="A4303" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B4303" t="n">
+        <v>183.85</v>
+      </c>
+      <c r="C4303" t="n">
+        <v>184.96</v>
+      </c>
+      <c r="D4303" t="n">
+        <v>183.18</v>
+      </c>
+      <c r="E4303" t="n">
+        <v>184.86</v>
+      </c>
+      <c r="F4303" t="n">
+        <v>5688704</v>
       </c>
     </row>
   </sheetData>
